--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.16731533949344</v>
+        <v>5.227188742667685</v>
       </c>
       <c r="D2" t="n">
-        <v>31.69008299305782</v>
+        <v>5.149638486371896</v>
       </c>
       <c r="E2" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F2" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.53050896595963</v>
+        <v>4.961207706968439</v>
       </c>
       <c r="D3" t="n">
-        <v>23.4599582332909</v>
+        <v>3.812243212909771</v>
       </c>
       <c r="E3" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F3" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.55572968863721</v>
+        <v>4.640306074403547</v>
       </c>
       <c r="D4" t="n">
-        <v>27.98988140737372</v>
+        <v>4.54835572869823</v>
       </c>
       <c r="E4" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F4" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.25883648602337</v>
+        <v>3.129560928978797</v>
       </c>
       <c r="D5" t="n">
-        <v>16.52794372040643</v>
+        <v>2.685790854566045</v>
       </c>
       <c r="E5" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F5" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.88754341023989</v>
+        <v>2.581725804163982</v>
       </c>
       <c r="D6" t="n">
-        <v>11.24154065258097</v>
+        <v>1.826750356044407</v>
       </c>
       <c r="E6" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F6" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.25098772746054</v>
+        <v>3.615785505712338</v>
       </c>
       <c r="D7" t="n">
-        <v>23.44793246859329</v>
+        <v>3.81028902614641</v>
       </c>
       <c r="E7" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F7" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.363486558428447</v>
+        <v>0.8715665657446228</v>
       </c>
       <c r="D8" t="n">
-        <v>21.64941390111374</v>
+        <v>3.518029758930982</v>
       </c>
       <c r="E8" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F8" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.50609665440988</v>
+        <v>3.332240706341605</v>
       </c>
       <c r="D9" t="n">
-        <v>20.86264604502507</v>
+        <v>3.390179982316573</v>
       </c>
       <c r="E9" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F9" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.37215289110281</v>
+        <v>3.960474844804207</v>
       </c>
       <c r="D10" t="n">
-        <v>29.33307541974156</v>
+        <v>4.766624755708003</v>
       </c>
       <c r="E10" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F10" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.78096476044775</v>
+        <v>8.25190677357276</v>
       </c>
       <c r="D11" t="n">
-        <v>55.63289870813344</v>
+        <v>9.040346040071684</v>
       </c>
       <c r="E11" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F11" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.9198827503596</v>
+        <v>3.074480946933435</v>
       </c>
       <c r="D12" t="n">
-        <v>19.36562017258167</v>
+        <v>3.146913278044521</v>
       </c>
       <c r="E12" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F12" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.6218855156719</v>
+        <v>3.838556396296684</v>
       </c>
       <c r="D13" t="n">
-        <v>23.30808939266402</v>
+        <v>3.787564526307903</v>
       </c>
       <c r="E13" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F13" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.19620305905941</v>
+        <v>1.656882997097154</v>
       </c>
       <c r="D14" t="n">
-        <v>9.741402842294235</v>
+        <v>1.582977961872813</v>
       </c>
       <c r="E14" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F14" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.94128389474047</v>
+        <v>3.565458632895326</v>
       </c>
       <c r="D15" t="n">
-        <v>21.50926834815169</v>
+        <v>3.49525610657465</v>
       </c>
       <c r="E15" t="n">
-        <v>10.38331924945633</v>
+        <v>1.687289378036654</v>
       </c>
       <c r="F15" t="n">
-        <v>10.59034774049561</v>
+        <v>1.720931507830536</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
